--- a/data/yk_metadata.xlsx
+++ b/data/yk_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/ykimura1_worldbank_org1/Documents/Desktop/PIP/NA_gap/Innovation hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_40479DC78F79A8D366075C52F37BD272CA418903" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{533B7F83-CC6C-4FD8-896B-172F60D2F1B2}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_40479DC78F79A8D366075C52F37BD272CA418903" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEBC0F44-2B85-40FD-A176-FC4FD4CCB298}"/>
   <bookViews>
-    <workbookView xWindow="-28695" yWindow="345" windowWidth="28800" windowHeight="15135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>citation</t>
   </si>
   <si>
-    <t>Included</t>
-  </si>
-  <si>
     <t>(Espen Beer Prydz, World Bank, eprydz@worldbank.org); (Umar Serajuddin, World Bank, userajuddin@worldbank.org); (Dean Jolliffe, World Bank, djolliffe@worldbank.org)</t>
   </si>
   <si>
@@ -112,26 +109,33 @@
     <t>gini, mean</t>
   </si>
   <si>
-    <t>1990-2022</t>
-  </si>
-  <si>
     <t>These countries contained data issues and were deemed outliers and hence excluded from analysis</t>
   </si>
   <si>
-    <t>Regional aggregates</t>
-  </si>
-  <si>
-    <t>BRN, ETH, GNQ, LSO, TON, MAC, MNP, UZB, GEO, LBN</t>
-  </si>
-  <si>
     <t>Does not account for underreporting of surveyed households.</t>
   </si>
   <si>
-    <t>Surveys often struggle to capture the living conditions of the richest of the population. This “missing rich” issue stems from a plethora of reasons, including item and unit nonresponse, accessibility issues (the rich more likely to live in hard to access places such as gated communities), and underreporting of their welfare. Whilst the lack of accurate representation of the living conditions of the rich in the survey distribution will not have a huge effect on the poverty rate, it can significantly underestimate the level of inequality within societies.
-The methodology here closely follows that of Chandy and Seidel (2017) and aims to tackle the issue of the “missing rich” by elongating the right-hand tail of the survey distribution using the information from the top decile of the survey distribution and attributing 50% of the gap between the national account mean and the survey mean to those in the extended tail. Thus, the assumption here is that the “missing rich” shares the Pareto parameter α (shape parameter) of those in the top decile that are observed in the survey and that 50% of the gap between the national account and the survey mean are attributable to the missing rich. This dataset provides information on the mean, poverty rate, and the Gini index calculated from attributing 50, 70, 90, and 100% of the gap between the survey mean and the following two national account variables: Household Final Consumption Expenditure (HFCE) and the Gross Domestic Product (GDP).</t>
-  </si>
-  <si>
     <t>poverty; inequality; top income correction</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>BRN, ETH, GNQ, LSO, TON, MAC, MNP, UZB, GEO, LBN, HND</t>
+  </si>
+  <si>
+    <t>1990-2024</t>
+  </si>
+  <si>
+    <t>Surveys often struggle to capture the living conditions of the richest of the population. This “missing rich” issue stems from a plethora of reasons, including item nonresponse (richer households more likely to not respond to welfare related modules of the survey) unit nonresponse (richer households more likely to not partake in surveys), accessibility issues (the rich more likely to live in hard to access places such as gated communities), and underreporting of their welfare. Further, there are consumption patterns and income sources that are specifically consumed or earned by the rich that surveys often do not capture fully (e.g. capital income). Whilst the lack of accurate representation of the living conditions of the rich in the survey distribution will not have a huge effect on the poverty rate, it can significantly underestimate the level of inequality within societies.
+One way in which this issue has been tackled is by utilizing the gap between the national account mean and the survey mean as a proxy for the "missing rich". Whilst [Lakner and Milanovic (2013)](https://doi.org/10.1596/1813-9450-6719) attributes the entire gap as the proxy for the missing top income in surveys, [Chandy and Seidel (2017)](https://www.brookings.edu/articles/how-much-do-we-really-know-about-inequality-within-countries-around-the-world/) argue that due to discrepancies in the definitions of income and consumption in surveys and national accounts, it is more justifiable to utilize a portion of the discrepancy between the survey mean and the nationla account mean. [Prydz, Jolliffe, and Serajuddin (2022)](https://doi.org/10.1111/roiw.12577) follow [Chandy and Seidel (2017)](https://www.brookings.edu/articles/how-much-do-we-really-know-about-inequality-within-countries-around-the-world/) and attribute 50% of the gap between Household Final Consumption Expenditure (HFCE) and the survey mean to the missing top. This analysis is also repeated by attributing 50% of the gap between GDP per capita and the survey mean.
+The aim of this approach is first to elongate the survey distirbution to capture the missing top by assuming that it follows a Pareto distribution; second is to attribute half of the survey-national accounts gap to the missing top represented by the extended portion of the survey distribution; and finally to reweight the survey distribution in light of the extended tail. In sum, this method imputes the "missing top" whilst maintaining the shape of the original survey distribution.
+For a more detailed explanation, please see [Chandy and Seidel (2017b)](https://www.brookings.edu/wp-content/uploads/2017/02/technical-appendix-02-13-17.pdf).
+We also provide adjusted distributions and the resulting Ginis for attributing different shares of the survey-HFCE gap to the missing top. The data is available at 5 percentage point increments (attributing 5% of the survey-HFCE gap to the extended top, all the way to attributing 100% of the gap). Further, whilst the focus is on bridging the gap between survey and HFCE, we also provide adjustments based on the survey-GDP gap.
+Additionally, whilst the choice of PPP (2017 vs 2021) will not affect the Gini estimates, the survey mean as well as the adjusted means will be different. All data is available for download for both PPPs.</t>
+  </si>
+  <si>
+    <t>These estimates are available for survey years only and as a result, no aggregate data is available</t>
   </si>
 </sst>
 </file>
@@ -163,18 +167,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -198,10 +196,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -218,6 +216,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,14 +509,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,7 +571,7 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -579,61 +581,86 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3">
         <v>44704</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H2" s="3">
-        <v>45707</v>
+        <v>45725</v>
       </c>
       <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
         <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
       </c>
       <c r="M2" t="s">
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
         <v>32</v>
       </c>
-      <c r="R2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
         <v>30</v>
       </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
       <c r="U2" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
